--- a/supplementary-materials/tables/Table_S05.xlsx
+++ b/supplementary-materials/tables/Table_S05.xlsx
@@ -215,7 +215,7 @@
     <t>Freeze the selected detection formula after end-to-end ecological-stability checks.</t>
   </si>
   <si>
-    <t>logit(pᵢₜⱼ) = α₀ + α₁z[log effort] + α₂z[log(1 + anthropogenic rate)] + α₃z[log(1 + frog rate)] + uᵢ.</t>
+    <t/>
   </si>
   <si>
     <t>Frozen</t>
